--- a/enrichissement-pharm/ig/StructureDefinition-fr-cda-dispositif-medical.xlsx
+++ b/enrichissement-pharm/ig/StructureDefinition-fr-cda-dispositif-medical.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7673" uniqueCount="625">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7673" uniqueCount="626">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-29T05:36:05+00:00</t>
+    <t>2026-07-29T08:04:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -96,7 +96,7 @@
     <t>FHIR Version</t>
   </si>
   <si>
-    <t>4.0.1</t>
+    <t>5.0.0</t>
   </si>
   <si>
     <t>Kind</t>
@@ -493,6 +493,10 @@
   </si>
   <si>
     <t>Supply.moodCode</t>
+  </si>
+  <si>
+    <t>- Si le DM a été dispensé : @moodCode='EVN'  
+ - Si le DM n’a pas encore été dispensé : @moodCode='INT'</t>
   </si>
   <si>
     <t xml:space="preserve">
@@ -4807,7 +4811,7 @@
         <v>156</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -4838,7 +4842,7 @@
       </c>
       <c r="Y25" s="2"/>
       <c r="Z25" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>75</v>
@@ -4876,10 +4880,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4905,10 +4909,10 @@
         <v>96</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -4959,7 +4963,7 @@
         <v>75</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>81</v>
@@ -4979,10 +4983,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5005,7 +5009,7 @@
         <v>75</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="L27" s="2"/>
       <c r="M27" s="2"/>
@@ -5034,11 +5038,11 @@
         <v>75</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="Y27" s="2"/>
       <c r="Z27" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>75</v>
@@ -5056,7 +5060,7 @@
         <v>75</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>81</v>
@@ -5076,10 +5080,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5102,10 +5106,10 @@
         <v>75</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="M28" s="2"/>
       <c r="N28" s="2"/>
@@ -5157,7 +5161,7 @@
         <v>75</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>81</v>
@@ -5177,10 +5181,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5278,17 +5282,17 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E30" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F30" t="s" s="2">
         <v>81</v>
@@ -5310,7 +5314,7 @@
       </c>
       <c r="L30" s="2"/>
       <c r="M30" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -5341,7 +5345,7 @@
       </c>
       <c r="Y30" s="2"/>
       <c r="Z30" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>75</v>
@@ -5359,7 +5363,7 @@
         <v>75</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>81</v>
@@ -5379,17 +5383,17 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E31" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F31" t="s" s="2">
         <v>81</v>
@@ -5407,11 +5411,11 @@
         <v>75</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="L31" s="2"/>
       <c r="M31" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -5462,7 +5466,7 @@
         <v>75</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>81</v>
@@ -5482,17 +5486,17 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E32" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F32" t="s" s="2">
         <v>81</v>
@@ -5514,7 +5518,7 @@
       </c>
       <c r="L32" s="2"/>
       <c r="M32" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -5545,7 +5549,7 @@
       </c>
       <c r="Y32" s="2"/>
       <c r="Z32" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>75</v>
@@ -5563,7 +5567,7 @@
         <v>75</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>81</v>
@@ -5583,17 +5587,17 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E33" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F33" t="s" s="2">
         <v>81</v>
@@ -5615,7 +5619,7 @@
       </c>
       <c r="L33" s="2"/>
       <c r="M33" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -5666,7 +5670,7 @@
         <v>75</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>81</v>
@@ -5686,17 +5690,17 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E34" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F34" t="s" s="2">
         <v>81</v>
@@ -5718,7 +5722,7 @@
       </c>
       <c r="L34" s="2"/>
       <c r="M34" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -5745,11 +5749,11 @@
         <v>75</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="Y34" s="2"/>
       <c r="Z34" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>75</v>
@@ -5767,7 +5771,7 @@
         <v>75</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>81</v>
@@ -5787,10 +5791,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5846,7 +5850,7 @@
       </c>
       <c r="Y35" s="2"/>
       <c r="Z35" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>75</v>
@@ -5864,7 +5868,7 @@
         <v>75</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>81</v>
@@ -5884,10 +5888,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5913,13 +5917,13 @@
         <v>103</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
@@ -5969,7 +5973,7 @@
         <v>75</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>81</v>
@@ -5989,17 +5993,17 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E37" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F37" t="s" s="2">
         <v>81</v>
@@ -6017,13 +6021,13 @@
         <v>75</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -6074,7 +6078,7 @@
         <v>75</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>81</v>
@@ -6094,17 +6098,17 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E38" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="F38" t="s" s="2">
         <v>81</v>
@@ -6122,11 +6126,11 @@
         <v>75</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="L38" s="2"/>
       <c r="M38" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -6177,7 +6181,7 @@
         <v>75</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>81</v>
@@ -6189,7 +6193,7 @@
         <v>75</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AK38" t="s" s="2">
         <v>75</v>
@@ -6197,10 +6201,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6226,10 +6230,10 @@
         <v>92</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -6260,7 +6264,7 @@
       </c>
       <c r="Y39" s="2"/>
       <c r="Z39" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>75</v>
@@ -6278,7 +6282,7 @@
         <v>75</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>81</v>
@@ -6298,10 +6302,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6324,13 +6328,13 @@
         <v>75</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -6381,7 +6385,7 @@
         <v>75</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>81</v>
@@ -6401,10 +6405,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6427,7 +6431,7 @@
         <v>75</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="L41" s="2"/>
       <c r="M41" s="2"/>
@@ -6456,11 +6460,11 @@
         <v>75</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="Y41" s="2"/>
       <c r="Z41" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>75</v>
@@ -6478,7 +6482,7 @@
         <v>75</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>81</v>
@@ -6498,10 +6502,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6524,13 +6528,13 @@
         <v>75</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -6581,7 +6585,7 @@
         <v>75</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>81</v>
@@ -6601,10 +6605,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6627,7 +6631,7 @@
         <v>75</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="L43" s="2"/>
       <c r="M43" s="2"/>
@@ -6680,7 +6684,7 @@
         <v>75</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>81</v>
@@ -6700,10 +6704,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6726,10 +6730,10 @@
         <v>75</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="M44" s="2"/>
       <c r="N44" s="2"/>
@@ -6781,7 +6785,7 @@
         <v>75</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>81</v>
@@ -6801,10 +6805,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6827,13 +6831,13 @@
         <v>75</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -6884,7 +6888,7 @@
         <v>75</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>81</v>
@@ -6904,10 +6908,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6930,7 +6934,7 @@
         <v>75</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="L46" s="2"/>
       <c r="M46" s="2"/>
@@ -6983,7 +6987,7 @@
         <v>75</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>81</v>
@@ -7003,10 +7007,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7104,10 +7108,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7205,10 +7209,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7306,10 +7310,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7407,10 +7411,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7510,10 +7514,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7613,10 +7617,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7716,10 +7720,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7819,10 +7823,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -7920,10 +7924,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -7957,7 +7961,7 @@
       </c>
       <c r="Q56" s="2"/>
       <c r="R56" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="S56" t="s" s="2">
         <v>75</v>
@@ -7979,7 +7983,7 @@
       </c>
       <c r="Y56" s="2"/>
       <c r="Z56" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>75</v>
@@ -7997,7 +8001,7 @@
         <v>75</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>81</v>
@@ -8017,10 +8021,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8043,7 +8047,7 @@
         <v>75</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="L57" s="2"/>
       <c r="M57" s="2"/>
@@ -8096,7 +8100,7 @@
         <v>75</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>76</v>
@@ -8116,10 +8120,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8142,7 +8146,7 @@
         <v>75</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="L58" s="2"/>
       <c r="M58" s="2"/>
@@ -8195,7 +8199,7 @@
         <v>75</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>81</v>
@@ -8215,10 +8219,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8241,7 +8245,7 @@
         <v>75</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="L59" s="2"/>
       <c r="M59" s="2"/>
@@ -8294,7 +8298,7 @@
         <v>75</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>81</v>
@@ -8314,10 +8318,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8340,13 +8344,13 @@
         <v>75</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -8397,7 +8401,7 @@
         <v>75</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>81</v>
@@ -8417,10 +8421,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8518,10 +8522,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8619,10 +8623,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -8720,10 +8724,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -8821,10 +8825,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -8924,10 +8928,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9027,10 +9031,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9130,10 +9134,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9233,10 +9237,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9334,10 +9338,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -9371,7 +9375,7 @@
       </c>
       <c r="Q70" s="2"/>
       <c r="R70" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="S70" t="s" s="2">
         <v>75</v>
@@ -9393,7 +9397,7 @@
       </c>
       <c r="Y70" s="2"/>
       <c r="Z70" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>75</v>
@@ -9411,7 +9415,7 @@
         <v>75</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>81</v>
@@ -9431,10 +9435,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -9457,7 +9461,7 @@
         <v>75</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="L71" s="2"/>
       <c r="M71" s="2"/>
@@ -9510,7 +9514,7 @@
         <v>75</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>81</v>
@@ -9530,10 +9534,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -9556,7 +9560,7 @@
         <v>75</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="L72" s="2"/>
       <c r="M72" s="2"/>
@@ -9609,7 +9613,7 @@
         <v>75</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>81</v>
@@ -9629,10 +9633,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -9673,7 +9677,7 @@
         <v>75</v>
       </c>
       <c r="S73" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="T73" t="s" s="2">
         <v>75</v>
@@ -9730,10 +9734,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -9756,11 +9760,11 @@
         <v>75</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="L74" s="2"/>
       <c r="M74" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" s="2"/>
@@ -9811,7 +9815,7 @@
         <v>75</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>81</v>
@@ -9831,10 +9835,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -9861,12 +9865,12 @@
       </c>
       <c r="L75" s="2"/>
       <c r="M75" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q75" s="2"/>
       <c r="R75" t="s" s="2">
@@ -9892,7 +9896,7 @@
       </c>
       <c r="Y75" s="2"/>
       <c r="Z75" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="AA75" t="s" s="2">
         <v>75</v>
@@ -9910,7 +9914,7 @@
         <v>75</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>81</v>
@@ -9930,17 +9934,17 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E76" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="F76" t="s" s="2">
         <v>81</v>
@@ -9958,11 +9962,11 @@
         <v>75</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="L76" s="2"/>
       <c r="M76" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="N76" s="2"/>
       <c r="O76" s="2"/>
@@ -10013,7 +10017,7 @@
         <v>75</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>81</v>
@@ -10033,17 +10037,17 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E77" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="F77" t="s" s="2">
         <v>81</v>
@@ -10061,11 +10065,11 @@
         <v>75</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="L77" s="2"/>
       <c r="M77" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
@@ -10116,7 +10120,7 @@
         <v>75</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>81</v>
@@ -10136,17 +10140,17 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E78" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="F78" t="s" s="2">
         <v>81</v>
@@ -10164,11 +10168,11 @@
         <v>75</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="L78" s="2"/>
       <c r="M78" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
@@ -10219,7 +10223,7 @@
         <v>75</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>81</v>
@@ -10239,17 +10243,17 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E79" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="F79" t="s" s="2">
         <v>81</v>
@@ -10267,11 +10271,11 @@
         <v>75</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="L79" s="2"/>
       <c r="M79" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" s="2"/>
@@ -10322,7 +10326,7 @@
         <v>75</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>81</v>
@@ -10342,10 +10346,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -10368,7 +10372,7 @@
         <v>75</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="L80" s="2"/>
       <c r="M80" s="2"/>
@@ -10421,7 +10425,7 @@
         <v>75</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>81</v>
@@ -10441,10 +10445,10 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -10467,7 +10471,7 @@
         <v>75</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="L81" s="2"/>
       <c r="M81" s="2"/>
@@ -10520,7 +10524,7 @@
         <v>75</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>76</v>
@@ -10540,10 +10544,10 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -10566,7 +10570,7 @@
         <v>75</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="L82" s="2"/>
       <c r="M82" s="2"/>
@@ -10619,7 +10623,7 @@
         <v>75</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>81</v>
@@ -10639,10 +10643,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -10665,7 +10669,7 @@
         <v>75</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="L83" s="2"/>
       <c r="M83" s="2"/>
@@ -10718,7 +10722,7 @@
         <v>75</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>81</v>
@@ -10738,10 +10742,10 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -10764,13 +10768,13 @@
         <v>75</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="N84" s="2"/>
       <c r="O84" s="2"/>
@@ -10821,7 +10825,7 @@
         <v>75</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>81</v>
@@ -10841,10 +10845,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -10942,10 +10946,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -11043,10 +11047,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -11144,10 +11148,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -11245,10 +11249,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -11348,10 +11352,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -11451,10 +11455,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -11554,10 +11558,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -11657,10 +11661,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -11758,10 +11762,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -11798,7 +11802,7 @@
         <v>75</v>
       </c>
       <c r="S94" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="T94" t="s" s="2">
         <v>75</v>
@@ -11817,7 +11821,7 @@
       </c>
       <c r="Y94" s="2"/>
       <c r="Z94" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="AA94" t="s" s="2">
         <v>75</v>
@@ -11835,7 +11839,7 @@
         <v>75</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>76</v>
@@ -11855,10 +11859,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -11892,7 +11896,7 @@
       </c>
       <c r="Q95" s="2"/>
       <c r="R95" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="S95" t="s" s="2">
         <v>75</v>
@@ -11914,7 +11918,7 @@
       </c>
       <c r="Y95" s="2"/>
       <c r="Z95" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AA95" t="s" s="2">
         <v>75</v>
@@ -11932,7 +11936,7 @@
         <v>75</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>81</v>
@@ -11952,10 +11956,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -11978,7 +11982,7 @@
         <v>75</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="L96" s="2"/>
       <c r="M96" s="2"/>
@@ -12031,7 +12035,7 @@
         <v>75</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>81</v>
@@ -12051,10 +12055,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -12077,7 +12081,7 @@
         <v>75</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="L97" s="2"/>
       <c r="M97" s="2"/>
@@ -12130,7 +12134,7 @@
         <v>75</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>81</v>
@@ -12150,10 +12154,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -12176,7 +12180,7 @@
         <v>75</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="L98" s="2"/>
       <c r="M98" s="2"/>
@@ -12229,7 +12233,7 @@
         <v>75</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>81</v>
@@ -12249,10 +12253,10 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -12275,7 +12279,7 @@
         <v>75</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="L99" s="2"/>
       <c r="M99" s="2"/>
@@ -12328,7 +12332,7 @@
         <v>75</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>76</v>
@@ -12348,10 +12352,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -12449,10 +12453,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -12550,10 +12554,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -12651,10 +12655,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -12752,10 +12756,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -12855,10 +12859,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -12958,10 +12962,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -13061,10 +13065,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -13164,10 +13168,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -13265,10 +13269,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -13298,14 +13302,14 @@
       <c r="N109" s="2"/>
       <c r="O109" s="2"/>
       <c r="P109" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="Q109" s="2"/>
       <c r="R109" t="s" s="2">
         <v>75</v>
       </c>
       <c r="S109" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="T109" t="s" s="2">
         <v>75</v>
@@ -13324,7 +13328,7 @@
       </c>
       <c r="Y109" s="2"/>
       <c r="Z109" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="AA109" t="s" s="2">
         <v>75</v>
@@ -13342,7 +13346,7 @@
         <v>75</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>81</v>
@@ -13362,10 +13366,10 @@
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -13391,10 +13395,10 @@
         <v>96</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="N110" s="2"/>
       <c r="O110" s="2"/>
@@ -13445,7 +13449,7 @@
         <v>75</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>81</v>
@@ -13465,10 +13469,10 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -13491,7 +13495,7 @@
         <v>75</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L111" s="2"/>
       <c r="M111" s="2"/>
@@ -13544,7 +13548,7 @@
         <v>75</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>81</v>
@@ -13564,10 +13568,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -13590,7 +13594,7 @@
         <v>75</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="L112" s="2"/>
       <c r="M112" s="2"/>
@@ -13619,11 +13623,11 @@
         <v>75</v>
       </c>
       <c r="X112" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="Y112" s="2"/>
       <c r="Z112" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AA112" t="s" s="2">
         <v>75</v>
@@ -13641,7 +13645,7 @@
         <v>75</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>81</v>
@@ -13661,10 +13665,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -13687,7 +13691,7 @@
         <v>75</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="L113" s="2"/>
       <c r="M113" s="2"/>
@@ -13740,7 +13744,7 @@
         <v>75</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>81</v>
@@ -13760,10 +13764,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -13786,7 +13790,7 @@
         <v>75</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="L114" s="2"/>
       <c r="M114" s="2"/>
@@ -13839,7 +13843,7 @@
         <v>75</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>81</v>
@@ -13859,10 +13863,10 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -13885,7 +13889,7 @@
         <v>75</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="L115" s="2"/>
       <c r="M115" s="2"/>
@@ -13938,7 +13942,7 @@
         <v>75</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>81</v>
@@ -13958,10 +13962,10 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -13984,13 +13988,13 @@
         <v>75</v>
       </c>
       <c r="K116" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="N116" s="2"/>
       <c r="O116" s="2"/>
@@ -14041,7 +14045,7 @@
         <v>75</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>81</v>
@@ -14061,10 +14065,10 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -14162,10 +14166,10 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -14263,10 +14267,10 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -14364,10 +14368,10 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -14465,10 +14469,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -14568,10 +14572,10 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -14671,10 +14675,10 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -14774,10 +14778,10 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -14877,10 +14881,10 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -14978,10 +14982,10 @@
     </row>
     <row r="126">
       <c r="A126" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -15011,14 +15015,14 @@
       <c r="N126" s="2"/>
       <c r="O126" s="2"/>
       <c r="P126" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Q126" s="2"/>
       <c r="R126" t="s" s="2">
         <v>75</v>
       </c>
       <c r="S126" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="T126" t="s" s="2">
         <v>75</v>
@@ -15037,7 +15041,7 @@
       </c>
       <c r="Y126" s="2"/>
       <c r="Z126" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AA126" t="s" s="2">
         <v>75</v>
@@ -15055,7 +15059,7 @@
         <v>75</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>81</v>
@@ -15075,10 +15079,10 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -15112,7 +15116,7 @@
       </c>
       <c r="Q127" s="2"/>
       <c r="R127" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="S127" t="s" s="2">
         <v>75</v>
@@ -15134,7 +15138,7 @@
       </c>
       <c r="Y127" s="2"/>
       <c r="Z127" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AA127" t="s" s="2">
         <v>75</v>
@@ -15152,7 +15156,7 @@
         <v>75</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>81</v>
@@ -15172,10 +15176,10 @@
     </row>
     <row r="128">
       <c r="A128" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -15198,13 +15202,13 @@
         <v>75</v>
       </c>
       <c r="K128" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="N128" s="2"/>
       <c r="O128" s="2"/>
@@ -15231,11 +15235,11 @@
         <v>75</v>
       </c>
       <c r="X128" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="Y128" s="2"/>
       <c r="Z128" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AA128" t="s" s="2">
         <v>75</v>
@@ -15253,7 +15257,7 @@
         <v>75</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>81</v>
@@ -15273,10 +15277,10 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -15374,10 +15378,10 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -15406,7 +15410,7 @@
       </c>
       <c r="L130" s="2"/>
       <c r="M130" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="N130" s="2"/>
       <c r="O130" s="2"/>
@@ -15457,7 +15461,7 @@
         <v>75</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>81</v>
@@ -15477,17 +15481,17 @@
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E131" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="F131" t="s" s="2">
         <v>81</v>
@@ -15509,7 +15513,7 @@
       </c>
       <c r="L131" s="2"/>
       <c r="M131" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="N131" s="2"/>
       <c r="O131" s="2"/>
@@ -15560,7 +15564,7 @@
         <v>75</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>81</v>
@@ -15580,17 +15584,17 @@
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E132" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="F132" t="s" s="2">
         <v>81</v>
@@ -15612,7 +15616,7 @@
       </c>
       <c r="L132" s="2"/>
       <c r="M132" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="N132" s="2"/>
       <c r="O132" s="2"/>
@@ -15663,7 +15667,7 @@
         <v>75</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>81</v>
@@ -15683,17 +15687,17 @@
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E133" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="F133" t="s" s="2">
         <v>81</v>
@@ -15715,7 +15719,7 @@
       </c>
       <c r="L133" s="2"/>
       <c r="M133" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="N133" s="2"/>
       <c r="O133" s="2"/>
@@ -15766,7 +15770,7 @@
         <v>75</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>81</v>
@@ -15786,17 +15790,17 @@
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E134" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="F134" t="s" s="2">
         <v>81</v>
@@ -15818,7 +15822,7 @@
       </c>
       <c r="L134" s="2"/>
       <c r="M134" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="N134" s="2"/>
       <c r="O134" s="2"/>
@@ -15869,7 +15873,7 @@
         <v>75</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>81</v>
@@ -15889,10 +15893,10 @@
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -15915,11 +15919,11 @@
         <v>75</v>
       </c>
       <c r="K135" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="L135" s="2"/>
       <c r="M135" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="N135" s="2"/>
       <c r="O135" s="2"/>
@@ -15970,7 +15974,7 @@
         <v>75</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>81</v>
@@ -15990,10 +15994,10 @@
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -16020,7 +16024,7 @@
       </c>
       <c r="L136" s="2"/>
       <c r="M136" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="N136" s="2"/>
       <c r="O136" s="2"/>
@@ -16071,7 +16075,7 @@
         <v>75</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>81</v>
@@ -16091,17 +16095,17 @@
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E137" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="F137" t="s" s="2">
         <v>81</v>
@@ -16119,11 +16123,11 @@
         <v>75</v>
       </c>
       <c r="K137" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="L137" s="2"/>
       <c r="M137" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="N137" s="2"/>
       <c r="O137" s="2"/>
@@ -16174,7 +16178,7 @@
         <v>75</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="AG137" t="s" s="2">
         <v>81</v>
@@ -16194,17 +16198,17 @@
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E138" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="F138" t="s" s="2">
         <v>81</v>
@@ -16222,11 +16226,11 @@
         <v>75</v>
       </c>
       <c r="K138" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="L138" s="2"/>
       <c r="M138" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="N138" s="2"/>
       <c r="O138" s="2"/>
@@ -16277,7 +16281,7 @@
         <v>75</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>81</v>
@@ -16297,17 +16301,17 @@
     </row>
     <row r="139">
       <c r="A139" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E139" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="F139" t="s" s="2">
         <v>81</v>
@@ -16325,13 +16329,13 @@
         <v>75</v>
       </c>
       <c r="K139" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="L139" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="M139" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="N139" s="2"/>
       <c r="O139" s="2"/>
@@ -16382,7 +16386,7 @@
         <v>75</v>
       </c>
       <c r="AF139" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AG139" t="s" s="2">
         <v>81</v>
@@ -16402,10 +16406,10 @@
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -16428,7 +16432,7 @@
         <v>75</v>
       </c>
       <c r="K140" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="L140" s="2"/>
       <c r="M140" s="2"/>
@@ -16457,11 +16461,11 @@
         <v>75</v>
       </c>
       <c r="X140" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="Y140" s="2"/>
       <c r="Z140" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AA140" t="s" s="2">
         <v>75</v>
@@ -16479,7 +16483,7 @@
         <v>75</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>81</v>
@@ -16499,10 +16503,10 @@
     </row>
     <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -16525,7 +16529,7 @@
         <v>75</v>
       </c>
       <c r="K141" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="L141" s="2"/>
       <c r="M141" s="2"/>
@@ -16554,11 +16558,11 @@
         <v>75</v>
       </c>
       <c r="X141" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="Y141" s="2"/>
       <c r="Z141" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="AA141" t="s" s="2">
         <v>75</v>
@@ -16576,7 +16580,7 @@
         <v>75</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>81</v>
@@ -16596,10 +16600,10 @@
     </row>
     <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -16622,7 +16626,7 @@
         <v>75</v>
       </c>
       <c r="K142" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="L142" s="2"/>
       <c r="M142" s="2"/>
@@ -16675,7 +16679,7 @@
         <v>75</v>
       </c>
       <c r="AF142" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AG142" t="s" s="2">
         <v>81</v>
@@ -16695,10 +16699,10 @@
     </row>
     <row r="143" hidden="true">
       <c r="A143" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -16721,7 +16725,7 @@
         <v>75</v>
       </c>
       <c r="K143" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="L143" s="2"/>
       <c r="M143" s="2"/>
@@ -16774,7 +16778,7 @@
         <v>75</v>
       </c>
       <c r="AF143" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="AG143" t="s" s="2">
         <v>81</v>
@@ -16794,10 +16798,10 @@
     </row>
     <row r="144" hidden="true">
       <c r="A144" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -16820,7 +16824,7 @@
         <v>75</v>
       </c>
       <c r="K144" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="L144" s="2"/>
       <c r="M144" s="2"/>
@@ -16861,7 +16865,7 @@
         <v>75</v>
       </c>
       <c r="AB144" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="AC144" s="2"/>
       <c r="AD144" t="s" s="2">
@@ -16871,7 +16875,7 @@
         <v>125</v>
       </c>
       <c r="AF144" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="AG144" t="s" s="2">
         <v>81</v>
@@ -16891,13 +16895,13 @@
     </row>
     <row r="145" hidden="true">
       <c r="A145" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="C145" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="D145" t="s" s="2">
         <v>75</v>
@@ -16919,10 +16923,10 @@
         <v>75</v>
       </c>
       <c r="K145" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="L145" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="M145" s="2"/>
       <c r="N145" s="2"/>
@@ -16974,7 +16978,7 @@
         <v>75</v>
       </c>
       <c r="AF145" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="AG145" t="s" s="2">
         <v>81</v>
@@ -16994,10 +16998,10 @@
     </row>
     <row r="146" hidden="true">
       <c r="A146" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -17095,10 +17099,10 @@
     </row>
     <row r="147" hidden="true">
       <c r="A147" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -17196,10 +17200,10 @@
     </row>
     <row r="148" hidden="true">
       <c r="A148" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -17297,10 +17301,10 @@
     </row>
     <row r="149" hidden="true">
       <c r="A149" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -17398,10 +17402,10 @@
     </row>
     <row r="150" hidden="true">
       <c r="A150" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -17501,10 +17505,10 @@
     </row>
     <row r="151" hidden="true">
       <c r="A151" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -17604,10 +17608,10 @@
     </row>
     <row r="152" hidden="true">
       <c r="A152" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
@@ -17707,10 +17711,10 @@
     </row>
     <row r="153" hidden="true">
       <c r="A153" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -17810,10 +17814,10 @@
     </row>
     <row r="154" hidden="true">
       <c r="A154" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
@@ -17911,10 +17915,10 @@
     </row>
     <row r="155" hidden="true">
       <c r="A155" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
@@ -17951,7 +17955,7 @@
         <v>75</v>
       </c>
       <c r="S155" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="T155" t="s" s="2">
         <v>75</v>
@@ -17970,7 +17974,7 @@
       </c>
       <c r="Y155" s="2"/>
       <c r="Z155" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="AA155" t="s" s="2">
         <v>75</v>
@@ -17988,7 +17992,7 @@
         <v>75</v>
       </c>
       <c r="AF155" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="AG155" t="s" s="2">
         <v>76</v>
@@ -18008,10 +18012,10 @@
     </row>
     <row r="156" hidden="true">
       <c r="A156" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
@@ -18038,7 +18042,7 @@
       </c>
       <c r="L156" s="2"/>
       <c r="M156" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="N156" s="2"/>
       <c r="O156" s="2"/>
@@ -18089,7 +18093,7 @@
         <v>75</v>
       </c>
       <c r="AF156" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="AG156" t="s" s="2">
         <v>81</v>
@@ -18109,10 +18113,10 @@
     </row>
     <row r="157" hidden="true">
       <c r="A157" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -18139,12 +18143,12 @@
       </c>
       <c r="L157" s="2"/>
       <c r="M157" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="N157" s="2"/>
       <c r="O157" s="2"/>
       <c r="P157" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="Q157" s="2"/>
       <c r="R157" t="s" s="2">
@@ -18190,7 +18194,7 @@
         <v>75</v>
       </c>
       <c r="AF157" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="AG157" t="s" s="2">
         <v>81</v>
@@ -18210,10 +18214,10 @@
     </row>
     <row r="158" hidden="true">
       <c r="A158" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
@@ -18289,7 +18293,7 @@
         <v>75</v>
       </c>
       <c r="AF158" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="AG158" t="s" s="2">
         <v>81</v>
@@ -18309,10 +18313,10 @@
     </row>
     <row r="159" hidden="true">
       <c r="A159" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
@@ -18335,7 +18339,7 @@
         <v>75</v>
       </c>
       <c r="K159" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="L159" s="2"/>
       <c r="M159" s="2"/>
@@ -18388,7 +18392,7 @@
         <v>75</v>
       </c>
       <c r="AF159" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="AG159" t="s" s="2">
         <v>81</v>
@@ -18408,10 +18412,10 @@
     </row>
     <row r="160" hidden="true">
       <c r="A160" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
@@ -18434,7 +18438,7 @@
         <v>75</v>
       </c>
       <c r="K160" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="L160" s="2"/>
       <c r="M160" s="2"/>
@@ -18487,7 +18491,7 @@
         <v>75</v>
       </c>
       <c r="AF160" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="AG160" t="s" s="2">
         <v>81</v>
@@ -18507,10 +18511,10 @@
     </row>
     <row r="161" hidden="true">
       <c r="A161" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
@@ -18533,7 +18537,7 @@
         <v>75</v>
       </c>
       <c r="K161" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="L161" s="2"/>
       <c r="M161" s="2"/>
@@ -18586,7 +18590,7 @@
         <v>75</v>
       </c>
       <c r="AF161" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="AG161" t="s" s="2">
         <v>81</v>
@@ -18606,10 +18610,10 @@
     </row>
     <row r="162" hidden="true">
       <c r="A162" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
@@ -18632,7 +18636,7 @@
         <v>75</v>
       </c>
       <c r="K162" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="L162" s="2"/>
       <c r="M162" s="2"/>
@@ -18685,7 +18689,7 @@
         <v>75</v>
       </c>
       <c r="AF162" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="AG162" t="s" s="2">
         <v>81</v>
@@ -18705,10 +18709,10 @@
     </row>
     <row r="163" hidden="true">
       <c r="A163" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
@@ -18731,7 +18735,7 @@
         <v>75</v>
       </c>
       <c r="K163" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="L163" s="2"/>
       <c r="M163" s="2"/>
@@ -18784,7 +18788,7 @@
         <v>75</v>
       </c>
       <c r="AF163" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="AG163" t="s" s="2">
         <v>81</v>
@@ -18804,10 +18808,10 @@
     </row>
     <row r="164" hidden="true">
       <c r="A164" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
@@ -18830,7 +18834,7 @@
         <v>75</v>
       </c>
       <c r="K164" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="L164" s="2"/>
       <c r="M164" s="2"/>
@@ -18883,7 +18887,7 @@
         <v>75</v>
       </c>
       <c r="AF164" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="AG164" t="s" s="2">
         <v>81</v>
@@ -18903,10 +18907,10 @@
     </row>
     <row r="165" hidden="true">
       <c r="A165" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
@@ -18929,7 +18933,7 @@
         <v>75</v>
       </c>
       <c r="K165" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="L165" s="2"/>
       <c r="M165" s="2"/>
@@ -18982,7 +18986,7 @@
         <v>75</v>
       </c>
       <c r="AF165" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="AG165" t="s" s="2">
         <v>81</v>
@@ -19002,10 +19006,10 @@
     </row>
     <row r="166" hidden="true">
       <c r="A166" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
@@ -19028,7 +19032,7 @@
         <v>75</v>
       </c>
       <c r="K166" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="L166" s="2"/>
       <c r="M166" s="2"/>
@@ -19081,7 +19085,7 @@
         <v>75</v>
       </c>
       <c r="AF166" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="AG166" t="s" s="2">
         <v>81</v>
@@ -19101,10 +19105,10 @@
     </row>
     <row r="167" hidden="true">
       <c r="A167" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
@@ -19127,7 +19131,7 @@
         <v>75</v>
       </c>
       <c r="K167" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="L167" s="2"/>
       <c r="M167" s="2"/>
@@ -19180,7 +19184,7 @@
         <v>75</v>
       </c>
       <c r="AF167" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="AG167" t="s" s="2">
         <v>81</v>
@@ -19200,10 +19204,10 @@
     </row>
     <row r="168" hidden="true">
       <c r="A168" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
@@ -19226,7 +19230,7 @@
         <v>75</v>
       </c>
       <c r="K168" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="L168" s="2"/>
       <c r="M168" s="2"/>
@@ -19279,7 +19283,7 @@
         <v>75</v>
       </c>
       <c r="AF168" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="AG168" t="s" s="2">
         <v>81</v>
@@ -19299,10 +19303,10 @@
     </row>
     <row r="169" hidden="true">
       <c r="A169" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="C169" s="2"/>
       <c r="D169" t="s" s="2">
@@ -19325,7 +19329,7 @@
         <v>75</v>
       </c>
       <c r="K169" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="L169" s="2"/>
       <c r="M169" s="2"/>
@@ -19378,7 +19382,7 @@
         <v>75</v>
       </c>
       <c r="AF169" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="AG169" t="s" s="2">
         <v>81</v>
@@ -19398,13 +19402,13 @@
     </row>
     <row r="170" hidden="true">
       <c r="A170" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="C170" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="D170" t="s" s="2">
         <v>75</v>
@@ -19426,10 +19430,10 @@
         <v>75</v>
       </c>
       <c r="K170" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="L170" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="M170" s="2"/>
       <c r="N170" s="2"/>
@@ -19481,7 +19485,7 @@
         <v>75</v>
       </c>
       <c r="AF170" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="AG170" t="s" s="2">
         <v>81</v>
@@ -19501,10 +19505,10 @@
     </row>
     <row r="171" hidden="true">
       <c r="A171" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
@@ -19602,10 +19606,10 @@
     </row>
     <row r="172" hidden="true">
       <c r="A172" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="C172" s="2"/>
       <c r="D172" t="s" s="2">
@@ -19703,10 +19707,10 @@
     </row>
     <row r="173" hidden="true">
       <c r="A173" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="C173" s="2"/>
       <c r="D173" t="s" s="2">
@@ -19804,10 +19808,10 @@
     </row>
     <row r="174" hidden="true">
       <c r="A174" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="C174" s="2"/>
       <c r="D174" t="s" s="2">
@@ -19905,10 +19909,10 @@
     </row>
     <row r="175" hidden="true">
       <c r="A175" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="C175" s="2"/>
       <c r="D175" t="s" s="2">
@@ -20008,10 +20012,10 @@
     </row>
     <row r="176" hidden="true">
       <c r="A176" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="C176" s="2"/>
       <c r="D176" t="s" s="2">
@@ -20111,10 +20115,10 @@
     </row>
     <row r="177" hidden="true">
       <c r="A177" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="C177" s="2"/>
       <c r="D177" t="s" s="2">
@@ -20214,10 +20218,10 @@
     </row>
     <row r="178" hidden="true">
       <c r="A178" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="C178" s="2"/>
       <c r="D178" t="s" s="2">
@@ -20317,10 +20321,10 @@
     </row>
     <row r="179" hidden="true">
       <c r="A179" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="C179" s="2"/>
       <c r="D179" t="s" s="2">
@@ -20418,10 +20422,10 @@
     </row>
     <row r="180" hidden="true">
       <c r="A180" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="C180" s="2"/>
       <c r="D180" t="s" s="2">
@@ -20458,7 +20462,7 @@
         <v>75</v>
       </c>
       <c r="S180" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="T180" t="s" s="2">
         <v>75</v>
@@ -20477,7 +20481,7 @@
       </c>
       <c r="Y180" s="2"/>
       <c r="Z180" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="AA180" t="s" s="2">
         <v>75</v>
@@ -20495,7 +20499,7 @@
         <v>75</v>
       </c>
       <c r="AF180" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="AG180" t="s" s="2">
         <v>76</v>
@@ -20515,10 +20519,10 @@
     </row>
     <row r="181" hidden="true">
       <c r="A181" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="C181" s="2"/>
       <c r="D181" t="s" s="2">
@@ -20545,7 +20549,7 @@
       </c>
       <c r="L181" s="2"/>
       <c r="M181" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="N181" s="2"/>
       <c r="O181" s="2"/>
@@ -20596,7 +20600,7 @@
         <v>75</v>
       </c>
       <c r="AF181" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="AG181" t="s" s="2">
         <v>81</v>
@@ -20616,10 +20620,10 @@
     </row>
     <row r="182" hidden="true">
       <c r="A182" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="C182" s="2"/>
       <c r="D182" t="s" s="2">
@@ -20646,12 +20650,12 @@
       </c>
       <c r="L182" s="2"/>
       <c r="M182" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="N182" s="2"/>
       <c r="O182" s="2"/>
       <c r="P182" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="Q182" s="2"/>
       <c r="R182" t="s" s="2">
@@ -20697,7 +20701,7 @@
         <v>75</v>
       </c>
       <c r="AF182" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="AG182" t="s" s="2">
         <v>81</v>
@@ -20717,10 +20721,10 @@
     </row>
     <row r="183" hidden="true">
       <c r="A183" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="C183" s="2"/>
       <c r="D183" t="s" s="2">
@@ -20796,7 +20800,7 @@
         <v>75</v>
       </c>
       <c r="AF183" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="AG183" t="s" s="2">
         <v>81</v>
@@ -20816,10 +20820,10 @@
     </row>
     <row r="184" hidden="true">
       <c r="A184" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="C184" s="2"/>
       <c r="D184" t="s" s="2">
@@ -20842,7 +20846,7 @@
         <v>75</v>
       </c>
       <c r="K184" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="L184" s="2"/>
       <c r="M184" s="2"/>
@@ -20895,7 +20899,7 @@
         <v>75</v>
       </c>
       <c r="AF184" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="AG184" t="s" s="2">
         <v>81</v>
@@ -20915,10 +20919,10 @@
     </row>
     <row r="185" hidden="true">
       <c r="A185" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="B185" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="C185" s="2"/>
       <c r="D185" t="s" s="2">
@@ -20941,7 +20945,7 @@
         <v>75</v>
       </c>
       <c r="K185" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="L185" s="2"/>
       <c r="M185" s="2"/>
@@ -20994,7 +20998,7 @@
         <v>75</v>
       </c>
       <c r="AF185" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="AG185" t="s" s="2">
         <v>81</v>
@@ -21014,10 +21018,10 @@
     </row>
     <row r="186" hidden="true">
       <c r="A186" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="B186" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="C186" s="2"/>
       <c r="D186" t="s" s="2">
@@ -21040,7 +21044,7 @@
         <v>75</v>
       </c>
       <c r="K186" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="L186" s="2"/>
       <c r="M186" s="2"/>
@@ -21093,7 +21097,7 @@
         <v>75</v>
       </c>
       <c r="AF186" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="AG186" t="s" s="2">
         <v>81</v>
@@ -21113,10 +21117,10 @@
     </row>
     <row r="187" hidden="true">
       <c r="A187" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="B187" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="C187" s="2"/>
       <c r="D187" t="s" s="2">
@@ -21139,7 +21143,7 @@
         <v>75</v>
       </c>
       <c r="K187" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="L187" s="2"/>
       <c r="M187" s="2"/>
@@ -21192,7 +21196,7 @@
         <v>75</v>
       </c>
       <c r="AF187" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="AG187" t="s" s="2">
         <v>81</v>
@@ -21212,10 +21216,10 @@
     </row>
     <row r="188" hidden="true">
       <c r="A188" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="B188" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="C188" s="2"/>
       <c r="D188" t="s" s="2">
@@ -21238,7 +21242,7 @@
         <v>75</v>
       </c>
       <c r="K188" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="L188" s="2"/>
       <c r="M188" s="2"/>
@@ -21291,7 +21295,7 @@
         <v>75</v>
       </c>
       <c r="AF188" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="AG188" t="s" s="2">
         <v>81</v>
@@ -21311,10 +21315,10 @@
     </row>
     <row r="189" hidden="true">
       <c r="A189" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="B189" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="C189" s="2"/>
       <c r="D189" t="s" s="2">
@@ -21337,7 +21341,7 @@
         <v>75</v>
       </c>
       <c r="K189" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="L189" s="2"/>
       <c r="M189" s="2"/>
@@ -21390,7 +21394,7 @@
         <v>75</v>
       </c>
       <c r="AF189" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="AG189" t="s" s="2">
         <v>81</v>
@@ -21410,10 +21414,10 @@
     </row>
     <row r="190" hidden="true">
       <c r="A190" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="B190" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="C190" s="2"/>
       <c r="D190" t="s" s="2">
@@ -21436,7 +21440,7 @@
         <v>75</v>
       </c>
       <c r="K190" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="L190" s="2"/>
       <c r="M190" s="2"/>
@@ -21489,7 +21493,7 @@
         <v>75</v>
       </c>
       <c r="AF190" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="AG190" t="s" s="2">
         <v>81</v>
@@ -21509,10 +21513,10 @@
     </row>
     <row r="191" hidden="true">
       <c r="A191" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="B191" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="C191" s="2"/>
       <c r="D191" t="s" s="2">
@@ -21535,7 +21539,7 @@
         <v>75</v>
       </c>
       <c r="K191" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="L191" s="2"/>
       <c r="M191" s="2"/>
@@ -21588,7 +21592,7 @@
         <v>75</v>
       </c>
       <c r="AF191" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="AG191" t="s" s="2">
         <v>81</v>
@@ -21608,10 +21612,10 @@
     </row>
     <row r="192" hidden="true">
       <c r="A192" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="B192" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="C192" s="2"/>
       <c r="D192" t="s" s="2">
@@ -21634,7 +21638,7 @@
         <v>75</v>
       </c>
       <c r="K192" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="L192" s="2"/>
       <c r="M192" s="2"/>
@@ -21687,7 +21691,7 @@
         <v>75</v>
       </c>
       <c r="AF192" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="AG192" t="s" s="2">
         <v>81</v>
@@ -21707,10 +21711,10 @@
     </row>
     <row r="193" hidden="true">
       <c r="A193" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="B193" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="C193" s="2"/>
       <c r="D193" t="s" s="2">
@@ -21733,7 +21737,7 @@
         <v>75</v>
       </c>
       <c r="K193" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="L193" s="2"/>
       <c r="M193" s="2"/>
@@ -21786,7 +21790,7 @@
         <v>75</v>
       </c>
       <c r="AF193" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="AG193" t="s" s="2">
         <v>81</v>
@@ -21806,10 +21810,10 @@
     </row>
     <row r="194" hidden="true">
       <c r="A194" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="B194" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="C194" s="2"/>
       <c r="D194" t="s" s="2">
@@ -21832,7 +21836,7 @@
         <v>75</v>
       </c>
       <c r="K194" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="L194" s="2"/>
       <c r="M194" s="2"/>
@@ -21885,7 +21889,7 @@
         <v>75</v>
       </c>
       <c r="AF194" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="AG194" t="s" s="2">
         <v>81</v>
@@ -21905,13 +21909,13 @@
     </row>
     <row r="195" hidden="true">
       <c r="A195" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="B195" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="C195" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="D195" t="s" s="2">
         <v>75</v>
@@ -21933,10 +21937,10 @@
         <v>75</v>
       </c>
       <c r="K195" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="L195" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="M195" s="2"/>
       <c r="N195" s="2"/>
@@ -21988,7 +21992,7 @@
         <v>75</v>
       </c>
       <c r="AF195" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="AG195" t="s" s="2">
         <v>81</v>
@@ -22008,10 +22012,10 @@
     </row>
     <row r="196" hidden="true">
       <c r="A196" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="B196" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C196" s="2"/>
       <c r="D196" t="s" s="2">
@@ -22109,10 +22113,10 @@
     </row>
     <row r="197" hidden="true">
       <c r="A197" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="B197" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="C197" s="2"/>
       <c r="D197" t="s" s="2">
@@ -22210,10 +22214,10 @@
     </row>
     <row r="198" hidden="true">
       <c r="A198" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="B198" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="C198" s="2"/>
       <c r="D198" t="s" s="2">
@@ -22311,10 +22315,10 @@
     </row>
     <row r="199" hidden="true">
       <c r="A199" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="B199" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="C199" s="2"/>
       <c r="D199" t="s" s="2">
@@ -22412,10 +22416,10 @@
     </row>
     <row r="200" hidden="true">
       <c r="A200" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="B200" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="C200" s="2"/>
       <c r="D200" t="s" s="2">
@@ -22515,10 +22519,10 @@
     </row>
     <row r="201" hidden="true">
       <c r="A201" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="B201" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="C201" s="2"/>
       <c r="D201" t="s" s="2">
@@ -22618,10 +22622,10 @@
     </row>
     <row r="202" hidden="true">
       <c r="A202" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="B202" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="C202" s="2"/>
       <c r="D202" t="s" s="2">
@@ -22721,10 +22725,10 @@
     </row>
     <row r="203" hidden="true">
       <c r="A203" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="B203" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="C203" s="2"/>
       <c r="D203" t="s" s="2">
@@ -22824,10 +22828,10 @@
     </row>
     <row r="204" hidden="true">
       <c r="A204" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="B204" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="C204" s="2"/>
       <c r="D204" t="s" s="2">
@@ -22925,10 +22929,10 @@
     </row>
     <row r="205" hidden="true">
       <c r="A205" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B205" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="C205" s="2"/>
       <c r="D205" t="s" s="2">
@@ -22965,7 +22969,7 @@
         <v>75</v>
       </c>
       <c r="S205" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="T205" t="s" s="2">
         <v>75</v>
@@ -22984,7 +22988,7 @@
       </c>
       <c r="Y205" s="2"/>
       <c r="Z205" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="AA205" t="s" s="2">
         <v>75</v>
@@ -23002,7 +23006,7 @@
         <v>75</v>
       </c>
       <c r="AF205" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="AG205" t="s" s="2">
         <v>76</v>
@@ -23022,10 +23026,10 @@
     </row>
     <row r="206" hidden="true">
       <c r="A206" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="B206" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="C206" s="2"/>
       <c r="D206" t="s" s="2">
@@ -23052,7 +23056,7 @@
       </c>
       <c r="L206" s="2"/>
       <c r="M206" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="N206" s="2"/>
       <c r="O206" s="2"/>
@@ -23103,7 +23107,7 @@
         <v>75</v>
       </c>
       <c r="AF206" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="AG206" t="s" s="2">
         <v>81</v>
@@ -23123,10 +23127,10 @@
     </row>
     <row r="207" hidden="true">
       <c r="A207" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="B207" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="C207" s="2"/>
       <c r="D207" t="s" s="2">
@@ -23153,12 +23157,12 @@
       </c>
       <c r="L207" s="2"/>
       <c r="M207" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="N207" s="2"/>
       <c r="O207" s="2"/>
       <c r="P207" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="Q207" s="2"/>
       <c r="R207" t="s" s="2">
@@ -23204,7 +23208,7 @@
         <v>75</v>
       </c>
       <c r="AF207" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="AG207" t="s" s="2">
         <v>81</v>
@@ -23224,10 +23228,10 @@
     </row>
     <row r="208" hidden="true">
       <c r="A208" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="B208" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="C208" s="2"/>
       <c r="D208" t="s" s="2">
@@ -23303,7 +23307,7 @@
         <v>75</v>
       </c>
       <c r="AF208" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="AG208" t="s" s="2">
         <v>81</v>
@@ -23323,10 +23327,10 @@
     </row>
     <row r="209" hidden="true">
       <c r="A209" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="B209" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="C209" s="2"/>
       <c r="D209" t="s" s="2">
@@ -23349,7 +23353,7 @@
         <v>75</v>
       </c>
       <c r="K209" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="L209" s="2"/>
       <c r="M209" s="2"/>
@@ -23402,7 +23406,7 @@
         <v>75</v>
       </c>
       <c r="AF209" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="AG209" t="s" s="2">
         <v>81</v>
@@ -23422,10 +23426,10 @@
     </row>
     <row r="210" hidden="true">
       <c r="A210" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="B210" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="C210" s="2"/>
       <c r="D210" t="s" s="2">
@@ -23448,7 +23452,7 @@
         <v>75</v>
       </c>
       <c r="K210" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="L210" s="2"/>
       <c r="M210" s="2"/>
@@ -23501,7 +23505,7 @@
         <v>75</v>
       </c>
       <c r="AF210" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="AG210" t="s" s="2">
         <v>81</v>
@@ -23521,10 +23525,10 @@
     </row>
     <row r="211" hidden="true">
       <c r="A211" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="B211" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="C211" s="2"/>
       <c r="D211" t="s" s="2">
@@ -23547,7 +23551,7 @@
         <v>75</v>
       </c>
       <c r="K211" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="L211" s="2"/>
       <c r="M211" s="2"/>
@@ -23600,7 +23604,7 @@
         <v>75</v>
       </c>
       <c r="AF211" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="AG211" t="s" s="2">
         <v>81</v>
@@ -23620,10 +23624,10 @@
     </row>
     <row r="212" hidden="true">
       <c r="A212" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="B212" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="C212" s="2"/>
       <c r="D212" t="s" s="2">
@@ -23646,7 +23650,7 @@
         <v>75</v>
       </c>
       <c r="K212" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="L212" s="2"/>
       <c r="M212" s="2"/>
@@ -23699,7 +23703,7 @@
         <v>75</v>
       </c>
       <c r="AF212" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="AG212" t="s" s="2">
         <v>81</v>
@@ -23719,10 +23723,10 @@
     </row>
     <row r="213" hidden="true">
       <c r="A213" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="B213" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="C213" s="2"/>
       <c r="D213" t="s" s="2">
@@ -23745,7 +23749,7 @@
         <v>75</v>
       </c>
       <c r="K213" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="L213" s="2"/>
       <c r="M213" s="2"/>
@@ -23798,7 +23802,7 @@
         <v>75</v>
       </c>
       <c r="AF213" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="AG213" t="s" s="2">
         <v>81</v>
@@ -23818,10 +23822,10 @@
     </row>
     <row r="214" hidden="true">
       <c r="A214" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="B214" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="C214" s="2"/>
       <c r="D214" t="s" s="2">
@@ -23844,7 +23848,7 @@
         <v>75</v>
       </c>
       <c r="K214" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="L214" s="2"/>
       <c r="M214" s="2"/>
@@ -23897,7 +23901,7 @@
         <v>75</v>
       </c>
       <c r="AF214" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="AG214" t="s" s="2">
         <v>81</v>
@@ -23917,10 +23921,10 @@
     </row>
     <row r="215" hidden="true">
       <c r="A215" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="B215" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="C215" s="2"/>
       <c r="D215" t="s" s="2">
@@ -23943,7 +23947,7 @@
         <v>75</v>
       </c>
       <c r="K215" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="L215" s="2"/>
       <c r="M215" s="2"/>
@@ -23996,7 +24000,7 @@
         <v>75</v>
       </c>
       <c r="AF215" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="AG215" t="s" s="2">
         <v>81</v>
@@ -24016,10 +24020,10 @@
     </row>
     <row r="216" hidden="true">
       <c r="A216" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="B216" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="C216" s="2"/>
       <c r="D216" t="s" s="2">
@@ -24042,7 +24046,7 @@
         <v>75</v>
       </c>
       <c r="K216" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="L216" s="2"/>
       <c r="M216" s="2"/>
@@ -24095,7 +24099,7 @@
         <v>75</v>
       </c>
       <c r="AF216" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="AG216" t="s" s="2">
         <v>81</v>
@@ -24115,10 +24119,10 @@
     </row>
     <row r="217" hidden="true">
       <c r="A217" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="B217" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="C217" s="2"/>
       <c r="D217" t="s" s="2">
@@ -24141,7 +24145,7 @@
         <v>75</v>
       </c>
       <c r="K217" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="L217" s="2"/>
       <c r="M217" s="2"/>
@@ -24194,7 +24198,7 @@
         <v>75</v>
       </c>
       <c r="AF217" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="AG217" t="s" s="2">
         <v>81</v>
@@ -24214,10 +24218,10 @@
     </row>
     <row r="218" hidden="true">
       <c r="A218" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="B218" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="C218" s="2"/>
       <c r="D218" t="s" s="2">
@@ -24240,7 +24244,7 @@
         <v>75</v>
       </c>
       <c r="K218" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="L218" s="2"/>
       <c r="M218" s="2"/>
@@ -24293,7 +24297,7 @@
         <v>75</v>
       </c>
       <c r="AF218" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="AG218" t="s" s="2">
         <v>81</v>
@@ -24313,10 +24317,10 @@
     </row>
     <row r="219" hidden="true">
       <c r="A219" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="B219" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="C219" s="2"/>
       <c r="D219" t="s" s="2">
@@ -24339,7 +24343,7 @@
         <v>75</v>
       </c>
       <c r="K219" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="L219" s="2"/>
       <c r="M219" s="2"/>
@@ -24392,7 +24396,7 @@
         <v>75</v>
       </c>
       <c r="AF219" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="AG219" t="s" s="2">
         <v>81</v>
@@ -24412,13 +24416,13 @@
     </row>
     <row r="220" hidden="true">
       <c r="A220" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="B220" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="C220" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="D220" t="s" s="2">
         <v>75</v>
@@ -24440,10 +24444,10 @@
         <v>75</v>
       </c>
       <c r="K220" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="L220" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="M220" s="2"/>
       <c r="N220" s="2"/>
@@ -24495,7 +24499,7 @@
         <v>75</v>
       </c>
       <c r="AF220" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="AG220" t="s" s="2">
         <v>81</v>
@@ -24515,10 +24519,10 @@
     </row>
     <row r="221" hidden="true">
       <c r="A221" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="B221" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C221" s="2"/>
       <c r="D221" t="s" s="2">
@@ -24616,10 +24620,10 @@
     </row>
     <row r="222" hidden="true">
       <c r="A222" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="B222" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="C222" s="2"/>
       <c r="D222" t="s" s="2">
@@ -24717,10 +24721,10 @@
     </row>
     <row r="223" hidden="true">
       <c r="A223" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="B223" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="C223" s="2"/>
       <c r="D223" t="s" s="2">
@@ -24818,10 +24822,10 @@
     </row>
     <row r="224" hidden="true">
       <c r="A224" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="B224" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="C224" s="2"/>
       <c r="D224" t="s" s="2">
@@ -24919,10 +24923,10 @@
     </row>
     <row r="225" hidden="true">
       <c r="A225" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="B225" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="C225" s="2"/>
       <c r="D225" t="s" s="2">
@@ -25022,10 +25026,10 @@
     </row>
     <row r="226" hidden="true">
       <c r="A226" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="B226" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="C226" s="2"/>
       <c r="D226" t="s" s="2">
@@ -25125,10 +25129,10 @@
     </row>
     <row r="227" hidden="true">
       <c r="A227" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="B227" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="C227" s="2"/>
       <c r="D227" t="s" s="2">
@@ -25228,10 +25232,10 @@
     </row>
     <row r="228" hidden="true">
       <c r="A228" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="B228" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="C228" s="2"/>
       <c r="D228" t="s" s="2">
@@ -25331,10 +25335,10 @@
     </row>
     <row r="229" hidden="true">
       <c r="A229" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="B229" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="C229" s="2"/>
       <c r="D229" t="s" s="2">
@@ -25432,10 +25436,10 @@
     </row>
     <row r="230" hidden="true">
       <c r="A230" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="B230" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="C230" s="2"/>
       <c r="D230" t="s" s="2">
@@ -25472,7 +25476,7 @@
         <v>75</v>
       </c>
       <c r="S230" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="T230" t="s" s="2">
         <v>75</v>
@@ -25491,7 +25495,7 @@
       </c>
       <c r="Y230" s="2"/>
       <c r="Z230" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="AA230" t="s" s="2">
         <v>75</v>
@@ -25509,7 +25513,7 @@
         <v>75</v>
       </c>
       <c r="AF230" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="AG230" t="s" s="2">
         <v>76</v>
@@ -25529,10 +25533,10 @@
     </row>
     <row r="231" hidden="true">
       <c r="A231" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="B231" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="C231" s="2"/>
       <c r="D231" t="s" s="2">
@@ -25559,7 +25563,7 @@
       </c>
       <c r="L231" s="2"/>
       <c r="M231" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="N231" s="2"/>
       <c r="O231" s="2"/>
@@ -25610,7 +25614,7 @@
         <v>75</v>
       </c>
       <c r="AF231" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="AG231" t="s" s="2">
         <v>81</v>
@@ -25630,10 +25634,10 @@
     </row>
     <row r="232" hidden="true">
       <c r="A232" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="B232" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="C232" s="2"/>
       <c r="D232" t="s" s="2">
@@ -25660,12 +25664,12 @@
       </c>
       <c r="L232" s="2"/>
       <c r="M232" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="N232" s="2"/>
       <c r="O232" s="2"/>
       <c r="P232" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="Q232" s="2"/>
       <c r="R232" t="s" s="2">
@@ -25711,7 +25715,7 @@
         <v>75</v>
       </c>
       <c r="AF232" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="AG232" t="s" s="2">
         <v>81</v>
@@ -25731,10 +25735,10 @@
     </row>
     <row r="233" hidden="true">
       <c r="A233" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="B233" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="C233" s="2"/>
       <c r="D233" t="s" s="2">
@@ -25810,7 +25814,7 @@
         <v>75</v>
       </c>
       <c r="AF233" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="AG233" t="s" s="2">
         <v>81</v>
@@ -25830,10 +25834,10 @@
     </row>
     <row r="234" hidden="true">
       <c r="A234" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="B234" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="C234" s="2"/>
       <c r="D234" t="s" s="2">
@@ -25856,7 +25860,7 @@
         <v>75</v>
       </c>
       <c r="K234" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="L234" s="2"/>
       <c r="M234" s="2"/>
@@ -25909,7 +25913,7 @@
         <v>75</v>
       </c>
       <c r="AF234" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="AG234" t="s" s="2">
         <v>81</v>
@@ -25929,10 +25933,10 @@
     </row>
     <row r="235" hidden="true">
       <c r="A235" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="B235" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="C235" s="2"/>
       <c r="D235" t="s" s="2">
@@ -25955,7 +25959,7 @@
         <v>75</v>
       </c>
       <c r="K235" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="L235" s="2"/>
       <c r="M235" s="2"/>
@@ -26008,7 +26012,7 @@
         <v>75</v>
       </c>
       <c r="AF235" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="AG235" t="s" s="2">
         <v>81</v>
@@ -26028,10 +26032,10 @@
     </row>
     <row r="236" hidden="true">
       <c r="A236" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="B236" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="C236" s="2"/>
       <c r="D236" t="s" s="2">
@@ -26054,7 +26058,7 @@
         <v>75</v>
       </c>
       <c r="K236" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="L236" s="2"/>
       <c r="M236" s="2"/>
@@ -26107,7 +26111,7 @@
         <v>75</v>
       </c>
       <c r="AF236" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="AG236" t="s" s="2">
         <v>81</v>
@@ -26127,10 +26131,10 @@
     </row>
     <row r="237" hidden="true">
       <c r="A237" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="B237" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="C237" s="2"/>
       <c r="D237" t="s" s="2">
@@ -26153,7 +26157,7 @@
         <v>75</v>
       </c>
       <c r="K237" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="L237" s="2"/>
       <c r="M237" s="2"/>
@@ -26206,7 +26210,7 @@
         <v>75</v>
       </c>
       <c r="AF237" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="AG237" t="s" s="2">
         <v>81</v>
@@ -26226,10 +26230,10 @@
     </row>
     <row r="238" hidden="true">
       <c r="A238" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="B238" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="C238" s="2"/>
       <c r="D238" t="s" s="2">
@@ -26252,7 +26256,7 @@
         <v>75</v>
       </c>
       <c r="K238" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="L238" s="2"/>
       <c r="M238" s="2"/>
@@ -26305,7 +26309,7 @@
         <v>75</v>
       </c>
       <c r="AF238" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="AG238" t="s" s="2">
         <v>81</v>
@@ -26325,10 +26329,10 @@
     </row>
     <row r="239" hidden="true">
       <c r="A239" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="B239" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="C239" s="2"/>
       <c r="D239" t="s" s="2">
@@ -26351,7 +26355,7 @@
         <v>75</v>
       </c>
       <c r="K239" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="L239" s="2"/>
       <c r="M239" s="2"/>
@@ -26404,7 +26408,7 @@
         <v>75</v>
       </c>
       <c r="AF239" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="AG239" t="s" s="2">
         <v>81</v>
@@ -26424,10 +26428,10 @@
     </row>
     <row r="240" hidden="true">
       <c r="A240" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="B240" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="C240" s="2"/>
       <c r="D240" t="s" s="2">
@@ -26450,7 +26454,7 @@
         <v>75</v>
       </c>
       <c r="K240" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="L240" s="2"/>
       <c r="M240" s="2"/>
@@ -26503,7 +26507,7 @@
         <v>75</v>
       </c>
       <c r="AF240" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="AG240" t="s" s="2">
         <v>81</v>
@@ -26523,10 +26527,10 @@
     </row>
     <row r="241" hidden="true">
       <c r="A241" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="B241" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="C241" s="2"/>
       <c r="D241" t="s" s="2">
@@ -26549,7 +26553,7 @@
         <v>75</v>
       </c>
       <c r="K241" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="L241" s="2"/>
       <c r="M241" s="2"/>
@@ -26602,7 +26606,7 @@
         <v>75</v>
       </c>
       <c r="AF241" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="AG241" t="s" s="2">
         <v>81</v>
@@ -26622,10 +26626,10 @@
     </row>
     <row r="242" hidden="true">
       <c r="A242" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="B242" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="C242" s="2"/>
       <c r="D242" t="s" s="2">
@@ -26648,7 +26652,7 @@
         <v>75</v>
       </c>
       <c r="K242" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="L242" s="2"/>
       <c r="M242" s="2"/>
@@ -26701,7 +26705,7 @@
         <v>75</v>
       </c>
       <c r="AF242" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="AG242" t="s" s="2">
         <v>81</v>
@@ -26721,10 +26725,10 @@
     </row>
     <row r="243" hidden="true">
       <c r="A243" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="B243" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="C243" s="2"/>
       <c r="D243" t="s" s="2">
@@ -26747,7 +26751,7 @@
         <v>75</v>
       </c>
       <c r="K243" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="L243" s="2"/>
       <c r="M243" s="2"/>
@@ -26800,7 +26804,7 @@
         <v>75</v>
       </c>
       <c r="AF243" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="AG243" t="s" s="2">
         <v>81</v>
@@ -26820,10 +26824,10 @@
     </row>
     <row r="244" hidden="true">
       <c r="A244" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="B244" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="C244" s="2"/>
       <c r="D244" t="s" s="2">
@@ -26846,7 +26850,7 @@
         <v>75</v>
       </c>
       <c r="K244" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="L244" s="2"/>
       <c r="M244" s="2"/>
@@ -26899,7 +26903,7 @@
         <v>75</v>
       </c>
       <c r="AF244" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="AG244" t="s" s="2">
         <v>81</v>
@@ -26919,10 +26923,10 @@
     </row>
     <row r="245" hidden="true">
       <c r="A245" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="B245" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="C245" s="2"/>
       <c r="D245" t="s" s="2">
@@ -26945,7 +26949,7 @@
         <v>75</v>
       </c>
       <c r="K245" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="L245" s="2"/>
       <c r="M245" s="2"/>
@@ -26998,7 +27002,7 @@
         <v>75</v>
       </c>
       <c r="AF245" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="AG245" t="s" s="2">
         <v>81</v>
@@ -27018,10 +27022,10 @@
     </row>
     <row r="246" hidden="true">
       <c r="A246" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="B246" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="C246" s="2"/>
       <c r="D246" t="s" s="2">
@@ -27044,7 +27048,7 @@
         <v>75</v>
       </c>
       <c r="K246" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="L246" s="2"/>
       <c r="M246" s="2"/>
@@ -27097,7 +27101,7 @@
         <v>75</v>
       </c>
       <c r="AF246" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="AG246" t="s" s="2">
         <v>81</v>
@@ -27117,10 +27121,10 @@
     </row>
     <row r="247" hidden="true">
       <c r="A247" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="B247" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="C247" s="2"/>
       <c r="D247" t="s" s="2">
@@ -27143,7 +27147,7 @@
         <v>75</v>
       </c>
       <c r="K247" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="L247" s="2"/>
       <c r="M247" s="2"/>
@@ -27196,7 +27200,7 @@
         <v>75</v>
       </c>
       <c r="AF247" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="AG247" t="s" s="2">
         <v>81</v>

--- a/enrichissement-pharm/ig/StructureDefinition-fr-cda-dispositif-medical.xlsx
+++ b/enrichissement-pharm/ig/StructureDefinition-fr-cda-dispositif-medical.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-29T08:04:35+00:00</t>
+    <t>2026-07-29T08:58:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/enrichissement-pharm/ig/StructureDefinition-fr-cda-dispositif-medical.xlsx
+++ b/enrichissement-pharm/ig/StructureDefinition-fr-cda-dispositif-medical.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-29T08:58:09+00:00</t>
+    <t>2026-07-29T09:37:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/enrichissement-pharm/ig/StructureDefinition-fr-cda-dispositif-medical.xlsx
+++ b/enrichissement-pharm/ig/StructureDefinition-fr-cda-dispositif-medical.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-29T09:37:21+00:00</t>
+    <t>2026-08-03T10:14:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
